--- a/docs/StructureDefinition-LTCBundleReferral.xlsx
+++ b/docs/StructureDefinition-LTCBundleReferral.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-28T05:34:23+08:00</t>
+    <t>2026-02-28T07:16:04+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LTCBundleReferral.xlsx
+++ b/docs/StructureDefinition-LTCBundleReferral.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-28T07:16:04+08:00</t>
+    <t>2026-02-28T23:13:53+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LTCBundleReferral.xlsx
+++ b/docs/StructureDefinition-LTCBundleReferral.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.4.1</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-28T23:13:53+08:00</t>
+    <t>2026-03-01T19:25:35+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LTCBundleReferral.xlsx
+++ b/docs/StructureDefinition-LTCBundleReferral.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-01T19:25:35+08:00</t>
+    <t>2026-03-02T02:26:08+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LTCBundleReferral.xlsx
+++ b/docs/StructureDefinition-LTCBundleReferral.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-02T02:26:08+08:00</t>
+    <t>2026-04-02T13:32:15+08:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1885,10 +1885,10 @@
 </t>
   </si>
   <si>
-    <t>Healthcare plan for patient or group</t>
-  </si>
-  <si>
-    <t>Describes the intention of how one or more practitioners intend to deliver care for a particular patient, group or community for a period of time, possibly limited to care for a specific condition or set of conditions.</t>
+    <t>特定照護目標下為一位患者或一群患者識別的活動、干預和結果計畫</t>
+  </si>
+  <si>
+    <t>描述為實現一個或多個目標而將為一位患者(或一群患者)進行的活動的計畫，包括診斷、監測、評估、治療、藥物治療、追蹤等。</t>
   </si>
   <si>
     <t>Act[classCode=PCPR, moodCode=INT]</t>

--- a/docs/StructureDefinition-LTCBundleReferral.xlsx
+++ b/docs/StructureDefinition-LTCBundleReferral.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T13:32:15+08:00</t>
+    <t>2026-04-03T21:17:06+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LTCBundleReferral.xlsx
+++ b/docs/StructureDefinition-LTCBundleReferral.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-03T21:17:06+08:00</t>
+    <t>2026-06-25T08:48:04+08:00</t>
   </si>
   <si>
     <t>Publisher</t>
